--- a/artfynd/A 56861-2020 artfynd.xlsx
+++ b/artfynd/A 56861-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126380339</v>
       </c>
       <c r="B2" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>126380340</v>
       </c>
       <c r="B3" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
